--- a/content/image_list.xlsx
+++ b/content/image_list.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🔶 2026-09-22 — 장면·장 수(27)·쓰는 곳·놓이는 자리는 하나씩 여쭈어 정했다(최종 확정 한마디는 대기). 지도 8장·문 정면 5장은 「무엇을 그릴지」가 아직 비어 있다 — 프롬프트 창에서 먼저 정의한다. 📝 표시는 확인 대기.</t>
+          <t>🔶 2026-09-22 — 장면·장 수(27 → 26 · 2026-09-23 빗장 EL-01을 뺐다)·쓰는 곳·놓이는 자리는 하나씩 여쭈어 정했다(최종 확정 한마디는 대기). ✅ 지도 8장은 「무엇을 그릴지」가 닫혔다(요소 17절 · 2026-09-23 · 각 줄 비고) — 사람의 차림만 프롬프트를 쓸 때 정한다. ✅ 문 정면 5장도 닫혔다(요소 17-10~17-14 · 2026-09-23 · 빗장 그림 없음). 📝 표시는 확인 대기.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>✅ 12절</t>
+          <t>✅ 12절(2026-09-23 새로 씀)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>⭐ 그림 속 구름·새를 내가 오려 내 움직인다(빈자리는 하늘 색으로) · 구름은 또렷한 덩어리로 · 위쪽 절반 여백(제목 자리) · 배경은 시작·캐릭터 선택이 함께 쓴다</t>
+          <t>⭐ 그림 속 구름만 내가 오려 내 움직인다(새는 그림에 그대로 · 움직이지 않는다 · 2026-09-23)(빈자리는 하늘 색으로) · 구름은 또렷한 덩어리로 · 위쪽 절반 여백(제목 자리) · 배경은 시작·캐릭터 선택이 함께 쓴다 · ✅ 2026-09-23 지도·문 결정에 맞췄다(요소 12절) — 궁 안 뜰마다 한 겹 행각 · 흙 마당(근정전 마당만 박석·돋운 삼도) · 영제교 돌난간+아치 둘 · 맨 아래는 아래로 곧게 뻗는 흙길 · 누각·천록·관청·현판 안 적음 · 구름 서너(움직임) · 새 서너(그대로)</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>BG-01 위에 얹는다 · 얼굴이 나오는 유일한 그림 · 지도 캐릭터(CH-03·04)와 같은 차림</t>
+          <t>BG-01 위에 얹는다 · 얼굴이 나오는 유일한 그림 · 지도 캐릭터(CH-03·04)와 같은 차림 · 바지는 청바지(2026-09-23 · 13절)</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · 지도 캐릭터(CH-03·04)와 같은 차림</t>
+          <t xml:space="preserve"> · 지도 캐릭터(CH-03·04)와 같은 차림 · 바지는 초록색 추리닝(2026-09-23 · 13절)</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · ✅ 무엇을 그릴지 정의 닫힘(요소 17-2 · 2026-09-22) — 1446년 고증: 월대·해치·동십자각 없음 · 흙길이 홍예문 셋에 닿는다 · 문지기 + 지나가는 사람 · 현판 光化門(깨지면 BG-15 글씨를 얹는다) · 좌우 궁성 담장만</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · ✅ 현판은 「弘禮門」(1446년 이름 · 요소 17-3 · 2026-09-22) · 알림창·미니맵도 「홍례문」 · ✅ 정의 닫힘(요소 17-3) — 아래쪽에 지나온 광화문 없음 · 문지기와 관리(백성 없음) · 좌우 행각(한 겹 · 1395년 원문 · 2026-09-23 담장에서 바꿈 · 요소 17-9) · 홍례문 2층 · 행각 양끝 각루 안 그림(요소 17-3·17-5 · 2026-09-23) · 바닥은 다져진 흙 마당(2026-09-23 · 요소 17-3·17-11)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · ✅ 정의 닫힘(요소 17-4 · 2026-09-23) — 돌다리(단순한 돌난간 · 아래 아치 둘) · 둑 위 돌짐승(천록) · 좌우 행각(한 겹) · 관리 드문드문 · 바닥은 다져진 흙 마당(2026-09-23 · 요소 17-4 결정 5)</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · ✅ 정의 닫힘(요소 17-5 · 2026-09-23) — 근정문 2층 · 현판 勤政門(깨지면 BG-18 글씨를 얹는다) · 좌우 행각(한 겹)이 양끝까지 한 줄(일화문·월화문·각루 안 그림) · 문지기 + 관리 · 바닥은 다져진 흙 마당(2026-09-23 · 요소 17-5 결정 7)</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · 근정문을 열고 들어서면 보이는 앞마당(삼도·품계석·기단 위 근정전) · 이 장에서 근정전 알림창(문 앞 화면 없음) · 🙋 2026-09-22</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · 이 장에서 근정전 알림창(문 앞 화면 없음) · ✅ 정의 닫힘(요소 17-6 · 2026-09-23) — 근정문을 열고 들어서면 보이는 앞마당 · 박석 · 조금 돋운 삼도가 근정전까지 · 2단 월대와 돌계단만(난간·돌짐승·향로·드므 없음) 위에 근정전 정면 5칸 2층 · 좌우 행각(한 겹) · 동서 행각 앞쪽 3분의 1에 2층 누각(융문루·융무루 · 행각 지붕 위로 조금 솟게) · 품계석 없음(1777년에 생김 · 알림창 글의 품계석은 그대로) · 관리 드문드문</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · ✅ 정의 닫힘(요소 17-7 · 2026-09-23) — 사정문 3칸 단층 · 현판 思政門(깨지면 BG-19 글씨를 얹는다) · 좌우 행각(한 겹) · 가운데 남북 복도(남천랑) 안 그림 · 문지기 + 관리 · 내시 · 댕기 한 궁녀 · 가체 쓴 상궁 · 바닥은 다져진 흙 마당(2026-09-23 · 요소 17-7 결정 6)</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · 여기 닿으면 알현 화면으로</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · 여기 닿으면 알현 화면으로 · ✅ 정의 닫힘(요소 17-8 · 2026-09-23) — 사정전 지금 모습(단층 · 낮은 기단) · 현판 思政殿(뭉개지면 내가 글꼴로 얹는다) · 좌우 행각(한 겹) · 곁방·만춘전·천추전 안 그림 · 관리 · 내시 · 댕기 한 궁녀 · 가체 쓴 상궁 · 바닥은 다져진 흙 마당(2026-09-23 · 요소 17-8 결정 5)</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 13-1절(선 그림 · 걸음 두 장은 선 그림을 본 뒤)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>이어폰을 목에 건 채 · 환복 없음(2026-09-22 🙋 "이거 빼자. 너무 많이 만들어야 해.") · 🧪 걸음 그림을 시도하면 +2</t>
+          <t>이어폰을 목에 건 채 · 환복 없음(2026-09-22 🙋 "이거 빼자. 너무 많이 만들어야 해.") · 🧪 걸음 그림을 시도하면 +2 · 바지는 청바지(2026-09-23 · 13절) · ✅ 정의 닫힘(요소 13-1 · 2026-09-23) — 두 발 나란히 곧게 선 뒷모습 · 소품이 뒤에서 보이게 · 걸음은 선 그림을 참고로</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 13-1절(선 그림 · 걸음 두 장은 선 그림을 본 뒤)</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>휴대폰을 든 채 · 환복 없음(2026-09-22 🙋 "이거 빼자. 너무 많이 만들어야 해.") · 🧪 걸음 그림을 시도하면 +2</t>
+          <t>휴대폰을 든 채 · 환복 없음(2026-09-22 🙋 "이거 빼자. 너무 많이 만들어야 해.") · 🧪 걸음 그림을 시도하면 +2 · 바지는 초록색 추리닝(2026-09-23 · 13절) · ✅ 정의 닫힘(요소 13-1 · 2026-09-23) — 두 발 나란히 곧게 선 뒷모습 · 소품이 뒤에서 보이게 · 걸음은 선 그림을 참고로</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 면과 빗장 자리를 비워 둔다 · 문짝 두 짝 · 빗장 1 · 홍예문 셋</t>
+          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 두 짝 · 홍예문 셋 · ⛔ 빗장 그림 없음(2026-09-23 · 요소 4) · ✅ 정의 닫힘(요소 17-10 · 2026-09-23) — 가운데 홍예문의 문짝이 열린다(내가 오린다) · 흙길 · 좌우 궁성 담장만(소나무 없음) · 사람 없음 · 정면 눈높이 · 지붕 위 하늘은 그림 높이의 6분의 1쯤 · 화풍은 지도와 같다 · 월대·해치·동십자각·누각의 종과 북 없음</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 면과 빗장 자리를 비워 둔다 · 문짝 두 짝 · 빗장 2</t>
+          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 두 짝 · ✅ 현판은 「弘禮門」(1446년 이름 · 요소 17-3 · 2026-09-22) · 알림창·미니맵도 「홍례문」 · ⛔ 빗장 그림 없음(2026-09-23 · 요소 4) · ✅ 정의 닫힘(요소 17-11 · 2026-09-23) — 3칸 2층 · 가운데 칸의 문짝이 열린다(내가 오린다) · 좌우 한 겹 행각(각루 안 그림) · 문 앞은 다져진 흙 마당 · 사람 없음 · 정면 눈높이 · 지붕 위 하늘 6분의 1쯤 · 화풍은 지도와 같다 · 소나무 없음</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 면과 빗장 자리를 비워 둔다 · 문짝 없음 · 다리를 건넌다 · 빗장 그림 없음 — 다리 중간에서 두 번 투명한 벽에 막힌다(코드 · 2026-09-22)</t>
+          <t>✅ 정의 닫힘(요소 17-12 · 2026-09-23) — 문짝·현판·빗장 없음 · 다리 머리(남쪽)에서 건너편을 곧게 본다: 다리가 화면 아래 가운데에서 위로 뻗고 바닥이 가운데로 둥글게 솟아 넘어간다 · 단순한 돌난간 · 개천이 가로로 흐르고 둑 위 천록이 양옆에 · 좌우 한 겹 행각 · 다리 너머로 근정문(2층)이 멀리 작게(현판 적지 않음) · 흙 마당 · 사람 없음 · 정면 눈높이 · 하늘 6분의 1쯤 · 화풍은 지도와 같다 · 소나무 없음 · 캐릭터는 ▲로 건너다 다리 중간에서 두 번 투명한 벽에 막힌다(코드 · 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 면과 빗장 자리를 비워 둔다 · 문짝 두 짝 · 빗장 3 · 2층 문루</t>
+          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 두 짝 · 2층 문루 · ⛔ 빗장 그림 없음(2026-09-23 · 요소 4) · ✅ 정의 닫힘(요소 17-13 · 2026-09-23) — 3칸 2층 · 현판 勤政門 · 가운데 칸의 문짝이 열린다(내가 오린다) · 좌우 한 겹 행각이 양끝까지(일화문·월화문·각루 안 그림) · 문 앞은 다져진 흙 마당 · 사람 없음 · 정면 눈높이 · 하늘 6분의 1쯤 · 화풍은 지도와 같다 · 소나무 없음</t>
         </is>
       </c>
     </row>
@@ -2061,14 +2061,14 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 면과 빗장 자리를 비워 둔다 · 문짝 두 짝 · 빗장 3</t>
+          <t>화면을 꽉 채운다(문루·현판·문짝·기단) · 현판 글씨를 그림에 그린다 · 정면·좌우 대칭 · 문짝 두 짝 · ⛔ 빗장 그림 없음(2026-09-23 · 요소 4) · ✅ 정의 닫힘(요소 17-14 · 2026-09-23) — 3칸 단층 · 현판 思政門 · 가운데 칸의 문짝이 열린다(내가 오린다) · 좌우 한 겹 행각(가운데 남천랑 안 그림) · 문 앞은 다져진 흙 마당 · 사람 없음 · 정면 눈높이 · 하늘 6분의 1쯤 · 화풍은 지도와 같다 · 소나무 없음</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2083,27 +2083,27 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>빗장 한 개</t>
+          <t>한지 — 본선 판 바탕</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>광화문·흥례문·근정문·사정문 (영제교에는 없다 — 투명한 벽 효과 · 2026-09-22)</t>
+          <t>자모 조합 판 · 점검 퀴즈 판 · 알림창 · 갈무리 판 · 서약서 판(크기에 맞춰 잘라 쓴다 · 2026-09-22 🙋)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>문짝 위에 가로로 · 광화문 1 · 흥례문 2 · 근정문 3 · 사정문 3 · 위에서부터 — 문마다 자리는 정면 그림을 뽑은 뒤 재서 정한다</t>
+          <t>판 바탕(74×38.5) · 알림창(64×33) · 갈무리(64×20.0) · 서약서(64×35.9) — 판 크기로 잘라 깐다 · 한지 넘김 앞뒷면</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>📝 가로로 긴 그림</t>
+          <t>판 비율 한 장</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>el_bolt</t>
+          <t>el_hanji_main</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>요소 4 · ⑤ 3번</t>
+          <t>10-4-1</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2123,14 +2123,14 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>여러 곳에 돌려 쓴다 · 코드로 미끄러져 빠진다 · 🧪 문 그림과 붙는지</t>
+          <t>빛깔은 뽑을 때 정한다 · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-03</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>한지 — 본선 판 바탕</t>
+          <t>한지 — 곁길 판 바탕(다른 장의 종이)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>자모 조합 판 · 점검 퀴즈 판 · 알림창 · 갈무리 판 · 서약서 판(크기에 맞춰 잘라 쓴다 · 2026-09-22 🙋)</t>
+          <t>힌트 퀴즈 판</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>판 바탕(74×38.5) · 알림창(64×33) · 갈무리(64×20.0) · 서약서(64×35.9) — 판 크기로 잘라 깐다 · 한지 넘김 앞뒷면</t>
+          <t>힌트 퀴즈 판 바탕 · 본선 판 위에 어긋나게(2.8)</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>el_hanji_main</t>
+          <t>el_hanji_side</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2185,49 +2185,49 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>빛깔은 뽑을 때 정한다 · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋)</t>
+          <t>본선 판 위에 어긋나게(2.8) · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>EL-03</t>
+          <t>BG-20</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>문 앞</t>
+          <t>알현 · 끝</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>게임 요소</t>
+          <t>배경</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>한지 — 곁길 판 바탕(다른 장의 종이)</t>
+          <t>사정전 안 — 일월오봉도 앞에 앉은 세종 · 앞에 드리운 발 · 발 너머로 비친다</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>힌트 퀴즈 판</t>
+          <t>알현 · 갈무리·서약서 판 뒤(어둡게)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>힌트 퀴즈 판 바탕 · 본선 판 위에 어긋나게(2.8)</t>
+          <t>화면 전체 · 갈무리·서약서 때는 어둡게</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>판 비율 한 장</t>
+          <t>가로 3:2 → 16:10</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>el_hanji_side</t>
+          <t>bg_audience</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>10-4-1</t>
+          <t>14절 · 14-1</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2247,59 +2247,59 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>본선 판 위에 어긋나게(2.8) · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋)</t>
+          <t>현판 없음(실내) · 세종 얼굴은 발이 가린다 · 발을 함께 그린다(2026-09-22 🙋)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>BG-20</t>
+          <t>CUT-01~08</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>알현 · 끝</t>
+          <t>문 앞</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>배경</t>
+          <t>파생</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>사정전 안 — 일월오봉도 앞에 앉은 세종 · 앞에 드리운 발 · 발 너머로 비친다</t>
+          <t>문짝 왼짝·오른짝 × 네 문(광화문·흥례문·근정문·사정문)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>알현 · 갈무리·서약서 판 뒤(어둡게)</t>
+          <t>문이 열릴 때</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>화면 전체 · 갈무리·서약서 때는 어둡게</t>
+          <t>정면 그림에서 오려 낸 그 자리 그대로 · 경첩 쪽을 축으로 돈다</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>가로 3:2 → 16:10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>bg_audience</t>
+          <t>cut_door_&lt;문&gt;_l / _r</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>14절 · 14-1</t>
+          <t>요소 3 · 10절</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -2309,129 +2309,67 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>현판 없음(실내) · 세종 얼굴은 발이 가린다 · 발을 함께 그린다(2026-09-22 🙋)</t>
+          <t>새로 뽑지 않는다 · 정면 그림에서 **내가** 오려 낸다(2026-09-22) · 틈 너머 빛은 코드</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>CUT-01~08</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>문 앞</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CUT-09~</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>표지</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>파생</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>문짝 왼짝·오른짝 × 네 문(광화문·흥례문·근정문·사정문)</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>문이 열릴 때</t>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>시작 화면 구름 조각 서너 덩어리(새는 오리지 않는다 · 2026-09-23)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>시작 화면에서 움직인다</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>정면 그림에서 오려 낸 그 자리 그대로 · 경첩 쪽을 축으로 돈다</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
+          <t>시작 화면 하늘 · 오려 낸 자리에서 출발해 흐른다</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>cut_door_&lt;문&gt;_l / _r</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>cut_cloud_n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>요소 3 · 10절</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>12절 · 2026-09-22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>새로 뽑지 않는다 · 정면 그림에서 **내가** 오려 낸다(2026-09-22) · 틈 너머 빛은 코드</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CUT-09~</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>표지</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>파생</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>시작 화면 구름 조각 서너 점 · 새 서너 마리</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>시작 화면에서 움직인다</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>시작 화면 하늘 · 오려 낸 자리에서 출발해 흐른다</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>cut_cloud_n / cut_bird_n</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>12절 · 2026-09-22</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>BG-01에서 내가 오려 낸다 · 🧪 어색하면 효과를 뺄지 여쭙는다</t>
         </is>
@@ -2608,12 +2546,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>빗장이 미끄러져 빠짐 · 문짝이 경첩으로 돎 · 틈 너머 빛</t>
+          <t>문짝이 경첩으로 돎 · 틈 너머 빛</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>그림(EL-01 · CUT)을 코드로 움직인다</t>
+          <t>그림(CUT)을 코드로 움직인다</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2689,7 +2627,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>시작 화면 구름·새 움직임</t>
+          <t>시작 화면 구름 움직임</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2849,7 +2787,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>문짝 두 짝의 테두리(오려 낼 선) · 경첩 축 · 빗장 걸리는 높이 · 캐릭터가 서는 자리 · ▲로 밀 때 막히는 선</t>
+          <t>문짝 두 짝의 테두리(오려 낼 선) · 경첩 축 · 캐릭터가 서는 자리 · ▲로 밀 때 막히는 선</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2900,7 +2838,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>구름·새 조각의 테두리 · 흐르는 길</t>
+          <t>구름 조각의 테두리 · 흐르는 길</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">

--- a/content/image_list.xlsx
+++ b/content/image_list.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🔶 2026-09-22 — 장면·장 수(27 → 26 · 2026-09-23 빗장 EL-01을 뺐다)·쓰는 곳·놓이는 자리는 하나씩 여쭈어 정했다(최종 확정 한마디는 대기). ✅ 지도 8장은 「무엇을 그릴지」가 닫혔다(요소 17절 · 2026-09-23 · 각 줄 비고) — 사람의 차림만 프롬프트를 쓸 때 정한다. ✅ 문 정면 5장도 닫혔다(요소 17-10~17-14 · 2026-09-23 · 빗장 그림 없음). 📝 표시는 확인 대기.</t>
+          <t>🔶 2026-09-22 — 장면·장 수(27 → 26 · 2026-09-23 빗장 EL-01을 뺐다)·쓰는 곳·놓이는 자리는 하나씩 여쭈어 정했다(최종 확정 한마디는 대기). ✅ 지도 8장은 「무엇을 그릴지」가 닫혔다(요소 17절 · 2026-09-23 · 각 줄 비고) — 사람 차림도 닫혔다(17-8-1). ✅ 문 정면 5장도 닫혔다(요소 17-10~17-14 · 2026-09-23 · 빗장 그림 없음). 📝 표시는 확인 대기. ✅ 2026-09-23 국문 프롬프트가 26장 모두 섰다(요소정의 각 절 · 이 표의 「국문 프롬프트」 열). 영문 최종본은 한 묶음으로.</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>없음(11절 옛 프롬프트는 폐기)</t>
+          <t>✅ 11-1절(2026-09-23)</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>책상 위(폰·공책·사극)는 그리지 않는다 · 0겹 현대 옷</t>
+          <t>~~책상 위(폰·공책·사극)는 그리지 않는다~~ → 책상 위는 공부하던 책상다운 것만(펼친 책·공책·연필 · 글씨는 흐린 줄) · 0겹 현대 옷 · ✅ 정의 닫힘(요소 11-1 · 2026-09-23) — 바로 뒤 눈높이 · 창밖 남색 밤 · 스탠드 노란 불빛 · 네 장 같은 방·구도 · 이어폰(서한글)·모자와 휴대폰(김세종)</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 11-1절(2026-09-23)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>BG-02와 같은 방·같은 구도로</t>
+          <t>BG-02와 같은 방·같은 구도로 · ✅ 정의 닫힘(요소 11-1 · 2026-09-23) — 바로 뒤 눈높이 · 창밖 남색 밤 · 스탠드 노란 불빛 · 네 장 같은 방·구도 · 이어폰(서한글)·모자와 휴대폰(김세종)</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 11-1절(2026-09-23)</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>이 위에서 컷 2 자막 글자가 떠올라 자모로 흩어진다(코드) · BG-02와 같은 방·같은 구도</t>
+          <t>이 위에서 컷 2 자막 글자가 떠올라 자모로 흩어진다(코드) · BG-02와 같은 방·같은 구도 · ✅ 정의 닫힘(요소 11-1 · 2026-09-23) — 바로 뒤 눈높이 · 창밖 남색 밤 · 스탠드 노란 불빛 · 네 장 같은 방·구도 · 이어폰(서한글)·모자와 휴대폰(김세종)</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 11-1절(2026-09-23)</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1071,7 +1071,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · ✅ 정의 닫힘(요소 11-1 · 2026-09-23) — 바로 뒤 눈높이 · 창밖 남색 밤 · 스탠드 노란 불빛 · 네 장 같은 방·구도 · 이어폰(서한글)·모자와 휴대폰(김세종)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1178,7 +1182,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1302,7 +1306,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1364,7 +1368,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1426,7 +1430,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1488,7 +1492,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1550,7 +1554,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1612,7 +1616,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1798,7 +1802,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1860,7 +1864,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1922,7 +1926,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1984,7 +1988,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2046,7 +2050,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 17-15(2026-09-23)</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2108,7 +2112,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 10-4-2(2026-09-23)</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>빛깔은 뽑을 때 정한다 · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋)</t>
+          <t>빛깔은 뽑을 때 정한다 · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋) · ✅ 정의 닫힘(요소 10-4-2) — 닥 섬유 결이 옅고 고르게 · 무늬·얼룩 없음 · 가장자리까지 꽉 찬 네모 · 빛깔은 옅은 미색</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2174,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 10-4-2(2026-09-23)</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>본선 판 위에 어긋나게(2.8) · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋)</t>
+          <t>본선 판 위에 어긋나게(2.8) · 한지 넘김의 앞면·뒷면에도 쓴다(2026-09-22 🙋) · ✅ 정의 닫힘(요소 10-4-2) — 본선과 같은 결·두께 · 빛깔은 옅은 치자빛(노랑) · 🙋 "나는 나가 좋아. 자연스러울 것 같아."</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>✅ 14-2(2026-09-23)</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2247,7 +2251,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>현판 없음(실내) · 세종 얼굴은 발이 가린다 · 발을 함께 그린다(2026-09-22 🙋)</t>
+          <t>현판 없음(실내) · 세종 얼굴은 발이 가린다 · 발을 함께 그린다(2026-09-22 🙋) · ✅ 정의 닫힘(요소 14-2 · 2026-09-23) — 일월오봉도(고증 예외) · 세종 차림은 꿈(BG-06)과 같다 · 대오리 발 + 남색 테두리(글자 무늬 없음) · 나무 마루 · 계단 높인 단 · 붉은 기둥 둘 · 정면 눈높이 · 아래 가운데 빈 마루 · 사람은 세종 한 분</t>
         </is>
       </c>
     </row>

--- a/content/image_list.xlsx
+++ b/content/image_list.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>🔶 2026-09-22 — 장면·장 수(27 → 26 · 2026-09-23 빗장 EL-01을 뺐다)·쓰는 곳·놓이는 자리는 하나씩 여쭈어 정했다(최종 확정 한마디는 대기). ✅ 지도 8장은 「무엇을 그릴지」가 닫혔다(요소 17절 · 2026-09-23 · 각 줄 비고) — 사람 차림도 닫혔다(17-8-1). ✅ 문 정면 5장도 닫혔다(요소 17-10~17-14 · 2026-09-23 · 빗장 그림 없음). 📝 표시는 확인 대기. ✅ 2026-09-23 국문 프롬프트가 26장 모두 섰다(요소정의 각 절 · 이 표의 「국문 프롬프트」 열). 영문 최종본은 한 묶음으로.</t>
+          <t>✅ 2026-09-26 최종 확정 — 26장(배경 20 · 캐릭터 4 · 게임 요소 2 · 오려 쓰는 CUT은 세지 않는다). 🙋 "그래. 이미 다 확정한 내용들 맞잖아." 이 목록이 그림 수의 SSOT다. 국문 프롬프트는 요소정의 각 절(이 표의 「국문 프롬프트」 열) · 쓸 그림 최종판(다시 그린 것)은 HANDOFF 🟩 「쓸 그림 — 최종」.</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>시작 · 캐릭터 선택(함께 쓴다)</t>
+          <t>시작 · 캐릭터 선택(함께 쓴다 · 캐릭터 선택에서는 흐리게 — 2026-09-26 디3)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>⭐ 그림 속 구름만 내가 오려 내 움직인다(새는 그림에 그대로 · 움직이지 않는다 · 2026-09-23)(빈자리는 하늘 색으로) · 구름은 또렷한 덩어리로 · 위쪽 절반 여백(제목 자리) · 배경은 시작·캐릭터 선택이 함께 쓴다 · ✅ 2026-09-23 지도·문 결정에 맞췄다(요소 12절) — 궁 안 뜰마다 한 겹 행각 · 흙 마당(근정전 마당만 박석·돋운 삼도) · 영제교 돌난간+아치 둘 · 맨 아래는 아래로 곧게 뻗는 흙길 · 누각·천록·관청·현판 안 적음 · 구름 서너(움직임) · 새 서너(그대로)</t>
+          <t>⭐ 그림 속 구름 셋 · 학 넷을 내가 오려 내 움직인다(2026-09-26 디2 · 빈자리는 하늘 색으로 · 오릴 자리와 초는 HANDOFF 디2) · 구름은 또렷한 덩어리로 · 하늘은 비워 둔다(구름·새가 움직이는 자리 · 제목은 시작 버튼 위 가운데 — 2026-09-26 디1) · 배경은 시작·캐릭터 선택이 함께 쓴다 · ✅ 2026-09-23 지도·문 결정에 맞췄다(요소 12절) — 궁 안 뜰마다 한 겹 행각 · 흙 마당(근정전 마당만 박석·돋운 삼도) · 영제교 돌난간+아치 둘 · 맨 아래는 아래로 곧게 뻗는 흙길 · 누각·천록·관청·현판 안 적음 · 구름 서너 · 새 서너(둘 다 움직임)</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>서한글 앞모습 · 0겹 현대 옷 · 전신</t>
+          <t>서한글 앞모습 · 현대 옷 · 전신</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>김세종 앞모습 · 0겹 현대 옷 · 전신</t>
+          <t>김세종 앞모습 · 현대 옷 · 전신</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>~~책상 위(폰·공책·사극)는 그리지 않는다~~ → 책상 위는 공부하던 책상다운 것만(펼친 책·공책·연필 · 글씨는 흐린 줄) · 0겹 현대 옷 · ✅ 정의 닫힘(요소 11-1 · 2026-09-23) — 바로 뒤 눈높이 · 창밖 남색 밤 · 스탠드 노란 불빛 · 네 장 같은 방·구도 · 이어폰(서한글)·모자와 휴대폰(김세종)</t>
+          <t>책상 위는 공부하던 책상다운 것만(펼친 책·공책·연필 · 글씨는 흐린 줄) · 현대 옷 · ✅ 정의 닫힘(요소 11-1 · 2026-09-23) — 바로 뒤 눈높이 · 창밖 남색 밤 · 스탠드 노란 불빛 · 네 장 같은 방·구도 · 이어폰(서한글)·모자와 휴대폰(김세종)</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>먹빛 어둠 속 곤룡포 뒷모습</t>
+          <t>구름 위 곤룡포 뒷모습과 일월오봉도 풍경 — 밝은 미색 바탕(2026-09-25 다시 그림)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>인물이 그림 안에 있다 · 자막 P-08 「어... 꿈인가? 근데 이 사람은???」</t>
+          <t>인물이 그림 안에 있다 · 자막은 다른 컷과 같은 먹색(2026-09-26) · 자막 P-08 「어... 꿈인가? 근데 이 사람은???」</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · 이 장에서 근정전 알림창(문 앞 화면 없음) · ✅ 정의 닫힘(요소 17-6 · 2026-09-23) — 근정문을 열고 들어서면 보이는 앞마당 · 박석 · 조금 돋운 삼도가 근정전까지 · 2단 월대와 돌계단만(난간·돌짐승·향로·드므 없음) 위에 근정전 정면 5칸 2층 · 좌우 행각(한 겹) · 동서 행각 앞쪽 3분의 1에 2층 누각(융문루·융무루 · 행각 지붕 위로 조금 솟게) · 품계석 없음(1777년에 생김 · 알림창 글의 품계석은 그대로) · 관리 드문드문</t>
+          <t>한 화면에 한 자리 · 평행사선 부감(의궤·동궐도 — 3D를 2D로 옮기는 왜곡을 알고 그린다) · 캐릭터를 얹는다 · 이 장에서 근정전 알림창(문 앞 화면 없음) · ✅ 정의 닫힘(요소 17-6 · 2026-09-23) — 근정문을 열고 들어서면 보이는 앞마당 · 박석 · 조금 돋운 삼도가 근정전까지 · 2단 월대와 돌계단만(난간·돌짐승·향로·드므 없음) 위에 근정전 정면 5칸 2층 · 좌우 행각(한 겹) · 동서 행각 앞쪽 3분의 1에 2층 누각(융문루·융무루 · 행각 지붕 위로 조금 솟게) · 품계석을 그린다(2026-09-25 · 요소 17-6 결정 1 · 알림창 M5-c와 맞음) · 관리 드문드문</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>✅ 13-1절(선 그림 · 걸음 두 장은 선 그림을 본 뒤)</t>
+          <t>✅ 13-1절(선 그림 · 걸음 그림은 뽑지 않음 · 2026-09-26 디8)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>✅ 13-1절(선 그림 · 걸음 두 장은 선 그림을 본 뒤)</t>
+          <t>✅ 13-1절(선 그림 · 걸음 그림은 뽑지 않음 · 2026-09-26 디8)</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>시작 화면 구름 조각 서너 덩어리(새는 오리지 않는다 · 2026-09-23)</t>
+          <t>시작 화면 구름 조각 셋 · 학 조각 넷(2026-09-26 디2)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2567,7 +2567,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>지도 장 넘김(위에서 내려옴) · 캐릭터 걷기(🧪 안 되면 미끄러짐) · 환복(그림 갈아 끼우기)</t>
+          <t>지도 장 넘김(위에서 내려옴) · 캐릭터 걷기(🧪 안 되면 미끄러짐)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
@@ -2631,7 +2631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>시작 화면 구름 움직임</t>
+          <t>시작 화면 구름·새 움직임</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>구름 조각의 테두리 · 흐르는 길</t>
+          <t>구름·학 조각의 테두리 · 흐르는 길(✅ 2026-09-26 목업에서 정함 · HANDOFF 디2)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
